--- a/docs/samples/census-report-sample.xlsx
+++ b/docs/samples/census-report-sample.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="108">
   <si>
     <t>AFP Medical Center</t>
   </si>
@@ -40,13 +40,13 @@
     <t>Not final – month still open</t>
   </si>
   <si>
-    <t>Generated 15-Oct-2026 10:00 by Sabryna Wyman Sr.</t>
-  </si>
-  <si>
-    <t>Grand totals (all categories)</t>
-  </si>
-  <si>
-    <t>Summary</t>
+    <t>Generated 15-Oct-2026 10:00 by Penelope Schneider</t>
+  </si>
+  <si>
+    <t>Patients and visits</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
   <si>
     <t>Patients</t>
@@ -55,22 +55,253 @@
     <t>Visits</t>
   </si>
   <si>
+    <t>OPD</t>
+  </si>
+  <si>
+    <t>ER</t>
+  </si>
+  <si>
+    <t>Admission</t>
+  </si>
+  <si>
+    <t>Total (all categories)</t>
+  </si>
+  <si>
+    <t>The total counts each patient once across all categories, so it can be less than the categories added together.</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Total patients</t>
+  </si>
+  <si>
+    <t>All categories</t>
+  </si>
+  <si>
+    <t>Age range by sex</t>
+  </si>
+  <si>
+    <t>Age range</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
-    <t>By category</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>OPD</t>
-  </si>
-  <si>
-    <t>ER</t>
-  </si>
-  <si>
-    <t>Admission</t>
+    <t>0–17</t>
+  </si>
+  <si>
+    <t>18–59</t>
+  </si>
+  <si>
+    <t>No bracket</t>
+  </si>
+  <si>
+    <t>Top 20 diagnoses (per visit, all categories)</t>
+  </si>
+  <si>
+    <t>Diagnosis</t>
+  </si>
+  <si>
+    <t>% of visits</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>Asthma</t>
+  </si>
+  <si>
+    <t>Dengue</t>
+  </si>
+  <si>
+    <t>Full list on each category page.</t>
+  </si>
+  <si>
+    <t>Branch of service</t>
+  </si>
+  <si>
+    <t>% of patients</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>AFP personnel</t>
+  </si>
+  <si>
+    <t>Others (not AFP personnel)</t>
+  </si>
+  <si>
+    <t>Ranks by branch</t>
+  </si>
+  <si>
+    <t>Branch / Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SGT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ENS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dependent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Retiree</t>
+  </si>
+  <si>
+    <t>New and returning patients</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>New (first visit ever in this period)</t>
+  </si>
+  <si>
+    <t>Returning (seen before)</t>
+  </si>
+  <si>
+    <t>Patients seen before this period are returning; the others had their first visit in it.</t>
+  </si>
+  <si>
+    <t>Daily census (visits)</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Total visits</t>
+  </si>
+  <si>
+    <t>01-Sep-2026 (Tue)</t>
+  </si>
+  <si>
+    <t>02-Sep-2026 (Wed)</t>
+  </si>
+  <si>
+    <t>03-Sep-2026 (Thu)</t>
+  </si>
+  <si>
+    <t>04-Sep-2026 (Fri)</t>
+  </si>
+  <si>
+    <t>05-Sep-2026 (Sat)</t>
+  </si>
+  <si>
+    <t>06-Sep-2026 (Sun)</t>
+  </si>
+  <si>
+    <t>07-Sep-2026 (Mon)</t>
+  </si>
+  <si>
+    <t>08-Sep-2026 (Tue)</t>
+  </si>
+  <si>
+    <t>09-Sep-2026 (Wed)</t>
+  </si>
+  <si>
+    <t>10-Sep-2026 (Thu)</t>
+  </si>
+  <si>
+    <t>11-Sep-2026 (Fri)</t>
+  </si>
+  <si>
+    <t>12-Sep-2026 (Sat)</t>
+  </si>
+  <si>
+    <t>13-Sep-2026 (Sun)</t>
+  </si>
+  <si>
+    <t>14-Sep-2026 (Mon)</t>
+  </si>
+  <si>
+    <t>15-Sep-2026 (Tue)</t>
+  </si>
+  <si>
+    <t>16-Sep-2026 (Wed)</t>
+  </si>
+  <si>
+    <t>17-Sep-2026 (Thu)</t>
+  </si>
+  <si>
+    <t>18-Sep-2026 (Fri)</t>
+  </si>
+  <si>
+    <t>19-Sep-2026 (Sat)</t>
+  </si>
+  <si>
+    <t>20-Sep-2026 (Sun)</t>
+  </si>
+  <si>
+    <t>21-Sep-2026 (Mon)</t>
+  </si>
+  <si>
+    <t>22-Sep-2026 (Tue)</t>
+  </si>
+  <si>
+    <t>23-Sep-2026 (Wed)</t>
+  </si>
+  <si>
+    <t>24-Sep-2026 (Thu)</t>
+  </si>
+  <si>
+    <t>25-Sep-2026 (Fri)</t>
+  </si>
+  <si>
+    <t>26-Sep-2026 (Sat)</t>
+  </si>
+  <si>
+    <t>27-Sep-2026 (Sun)</t>
+  </si>
+  <si>
+    <t>28-Sep-2026 (Mon)</t>
+  </si>
+  <si>
+    <t>29-Sep-2026 (Tue)</t>
+  </si>
+  <si>
+    <t>30-Sep-2026 (Wed)</t>
+  </si>
+  <si>
+    <t>Busiest day: 04-Sep-2026 (Fri), 2 visits.</t>
+  </si>
+  <si>
+    <t>Compared with the previous period</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>This period</t>
+  </si>
+  <si>
+    <t>August 2026</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Change %</t>
+  </si>
+  <si>
+    <t>The previous period is the one of the same length just before this one.</t>
   </si>
   <si>
     <t>Prepared by · Admission / Admin Office</t>
@@ -91,93 +322,43 @@
     <t>Patients and Visits</t>
   </si>
   <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Age range</t>
-  </si>
-  <si>
-    <t>0–17</t>
-  </si>
-  <si>
-    <t>18–59</t>
-  </si>
-  <si>
     <t>Diagnosis (per visit)</t>
   </si>
   <si>
-    <t>Diagnosis</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 12 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 3 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 6 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 9 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
     <t>Branch of service and rank</t>
   </si>
   <si>
-    <t>Branch / Rank</t>
-  </si>
-  <si>
-    <t>Army</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    CPL</t>
+    <t>Patients with no earlier OPD visit are new; the others were seen in OPD before this period.</t>
+  </si>
+  <si>
+    <t>Busiest day: 05-Sep-2026 (Sat), 2 visits.</t>
   </si>
   <si>
     <t>Monthly Patient Census Report – ER</t>
   </si>
   <si>
-    <t>Sample diagnosis number 1 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 10 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 11 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 2 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 4 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 5 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 7 with a rather long descriptive name that wraps</t>
-  </si>
-  <si>
-    <t>Sample diagnosis number 8 with a rather long descriptive name that wraps</t>
+    <t>Patients with no earlier ER visit are new; the others were seen in ER before this period.</t>
   </si>
   <si>
     <t>Monthly Patient Census Report – Admission</t>
+  </si>
+  <si>
+    <t>Patients with no earlier Admission visit are new; the others were seen in Admission before this period.</t>
+  </si>
+  <si>
+    <t>Busiest day: 06-Sep-2026 (Sun), 1 visit.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="166" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;;0.0&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -241,6 +422,15 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -298,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="27">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -319,13 +509,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="3" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
@@ -337,6 +521,45 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="3" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="3" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="164" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="3" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="166" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="166" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -785,51 +1008,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="41" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12" customWidth="true" style="0"/>
+    <col min="3" max="3" width="13" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="42"/>
-    <row r="2" spans="1:3" customHeight="1" ht="24">
+    <row r="1" spans="1:5" customHeight="1" ht="42"/>
+    <row r="2" spans="1:5" customHeight="1" ht="24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" customHeight="1" ht="19">
+    <row r="3" spans="1:5" customHeight="1" ht="19">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" customHeight="1" ht="21">
+    <row r="4" spans="1:5" customHeight="1" ht="21">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" customHeight="1" ht="18">
+    <row r="5" spans="1:5" customHeight="1" ht="18">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customHeight="1" ht="18">
+    <row r="6" spans="1:5" customHeight="1" ht="18">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customHeight="1" ht="18">
+    <row r="7" spans="1:5" customHeight="1" ht="18">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" customHeight="1" ht="22">
+    <row r="9" spans="1:5" customHeight="1" ht="22">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" customHeight="1" ht="20">
+    <row r="10" spans="1:5" customHeight="1" ht="20">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -840,94 +1065,1109 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:5">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="9">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11">
+        <v>3</v>
+      </c>
+      <c r="C12" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="9">
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13">
+        <v>5</v>
+      </c>
+      <c r="C14" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="30">
+      <c r="A15" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="22">
+      <c r="A17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="20">
+      <c r="A18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="9">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="11">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" customHeight="1" ht="22">
-      <c r="A13" s="5" t="s">
+      <c r="B21" s="9">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13">
+        <v>3</v>
+      </c>
+      <c r="C22" s="13">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="22">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="20">
+      <c r="A25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="11">
+        <v>2</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="9">
+        <v>1</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="13">
+        <v>3</v>
+      </c>
+      <c r="C29" s="13">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="22">
+      <c r="A31" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="20">
+      <c r="A32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="9">
+        <v>4</v>
+      </c>
+      <c r="C33" s="15">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="11">
+        <v>2</v>
+      </c>
+      <c r="C34" s="16">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="9">
+        <v>1</v>
+      </c>
+      <c r="C35" s="15">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" customHeight="1" ht="15">
+      <c r="A36" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" customHeight="1" ht="22">
+      <c r="A38" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" customHeight="1" ht="20">
+      <c r="A39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="9">
+        <v>2</v>
+      </c>
+      <c r="C40" s="15">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="11">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="9">
+        <v>2</v>
+      </c>
+      <c r="C42" s="15">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="13">
+        <v>3</v>
+      </c>
+      <c r="C43" s="17">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="19">
+        <v>2</v>
+      </c>
+      <c r="C44" s="20">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" customHeight="1" ht="22">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" customHeight="1" ht="20">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" customHeight="1" ht="22">
+      <c r="A57" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" customHeight="1" ht="20">
+      <c r="A58" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" s="9">
+        <v>3</v>
+      </c>
+      <c r="C59" s="15">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" s="11">
+        <v>2</v>
+      </c>
+      <c r="C60" s="16">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="19">
+        <v>5</v>
+      </c>
+      <c r="C61" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" customHeight="1" ht="15">
+      <c r="A62" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" customHeight="1" ht="22">
+      <c r="A64" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" customHeight="1" ht="20">
+      <c r="A65" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" customHeight="1" ht="20">
-      <c r="A14" s="6" t="s">
+      <c r="D65" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="E65" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B66" s="9">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9">
+        <v>0</v>
+      </c>
+      <c r="D66" s="9">
+        <v>0</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="11">
+        <v>0</v>
+      </c>
+      <c r="C67" s="11">
+        <v>0</v>
+      </c>
+      <c r="D67" s="11">
+        <v>0</v>
+      </c>
+      <c r="E67" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="9">
+        <v>0</v>
+      </c>
+      <c r="C68" s="9">
+        <v>1</v>
+      </c>
+      <c r="D68" s="9">
+        <v>0</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="11">
+        <v>0</v>
+      </c>
+      <c r="C69" s="11">
+        <v>2</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0</v>
+      </c>
+      <c r="E69" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="9">
+        <v>2</v>
+      </c>
+      <c r="C70" s="9">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0</v>
+      </c>
+      <c r="E70" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B71" s="11">
+        <v>0</v>
+      </c>
+      <c r="C71" s="11">
+        <v>0</v>
+      </c>
+      <c r="D71" s="11">
+        <v>1</v>
+      </c>
+      <c r="E71" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="9">
+        <v>0</v>
+      </c>
+      <c r="C72" s="9">
+        <v>0</v>
+      </c>
+      <c r="D72" s="9">
+        <v>0</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="11">
+        <v>0</v>
+      </c>
+      <c r="C73" s="11">
+        <v>0</v>
+      </c>
+      <c r="D73" s="11">
+        <v>0</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="9">
+        <v>0</v>
+      </c>
+      <c r="C74" s="9">
+        <v>0</v>
+      </c>
+      <c r="D74" s="9">
+        <v>0</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="11">
+        <v>0</v>
+      </c>
+      <c r="C75" s="11">
+        <v>1</v>
+      </c>
+      <c r="D75" s="11">
+        <v>0</v>
+      </c>
+      <c r="E75" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="9">
+        <v>0</v>
+      </c>
+      <c r="C76" s="9">
+        <v>0</v>
+      </c>
+      <c r="D76" s="9">
+        <v>0</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="11">
+        <v>0</v>
+      </c>
+      <c r="C77" s="11">
+        <v>0</v>
+      </c>
+      <c r="D77" s="11">
+        <v>0</v>
+      </c>
+      <c r="E77" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="9">
+        <v>0</v>
+      </c>
+      <c r="C78" s="9">
+        <v>0</v>
+      </c>
+      <c r="D78" s="9">
+        <v>0</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B79" s="11">
+        <v>0</v>
+      </c>
+      <c r="C79" s="11">
+        <v>0</v>
+      </c>
+      <c r="D79" s="11">
+        <v>0</v>
+      </c>
+      <c r="E79" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="9">
+        <v>0</v>
+      </c>
+      <c r="C80" s="9">
+        <v>0</v>
+      </c>
+      <c r="D80" s="9">
+        <v>0</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81" s="11">
+        <v>0</v>
+      </c>
+      <c r="C81" s="11">
+        <v>0</v>
+      </c>
+      <c r="D81" s="11">
+        <v>0</v>
+      </c>
+      <c r="E81" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82" s="9">
+        <v>0</v>
+      </c>
+      <c r="C82" s="9">
+        <v>0</v>
+      </c>
+      <c r="D82" s="9">
+        <v>0</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="11">
+        <v>0</v>
+      </c>
+      <c r="C83" s="11">
+        <v>0</v>
+      </c>
+      <c r="D83" s="11">
+        <v>0</v>
+      </c>
+      <c r="E83" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="9">
+        <v>0</v>
+      </c>
+      <c r="C84" s="9">
+        <v>0</v>
+      </c>
+      <c r="D84" s="9">
+        <v>0</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="11">
+        <v>0</v>
+      </c>
+      <c r="C85" s="11">
+        <v>0</v>
+      </c>
+      <c r="D85" s="11">
+        <v>0</v>
+      </c>
+      <c r="E85" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="9">
+        <v>0</v>
+      </c>
+      <c r="C86" s="9">
+        <v>0</v>
+      </c>
+      <c r="D86" s="9">
+        <v>0</v>
+      </c>
+      <c r="E86" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="11">
+        <v>0</v>
+      </c>
+      <c r="C87" s="11">
+        <v>0</v>
+      </c>
+      <c r="D87" s="11">
+        <v>0</v>
+      </c>
+      <c r="E87" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B88" s="9">
+        <v>0</v>
+      </c>
+      <c r="C88" s="9">
+        <v>0</v>
+      </c>
+      <c r="D88" s="9">
+        <v>0</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B89" s="11">
+        <v>0</v>
+      </c>
+      <c r="C89" s="11">
+        <v>0</v>
+      </c>
+      <c r="D89" s="11">
+        <v>0</v>
+      </c>
+      <c r="E89" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B90" s="9">
+        <v>0</v>
+      </c>
+      <c r="C90" s="9">
+        <v>0</v>
+      </c>
+      <c r="D90" s="9">
+        <v>0</v>
+      </c>
+      <c r="E90" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B91" s="11">
+        <v>0</v>
+      </c>
+      <c r="C91" s="11">
+        <v>0</v>
+      </c>
+      <c r="D91" s="11">
+        <v>0</v>
+      </c>
+      <c r="E91" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B92" s="9">
+        <v>0</v>
+      </c>
+      <c r="C92" s="9">
+        <v>0</v>
+      </c>
+      <c r="D92" s="9">
+        <v>0</v>
+      </c>
+      <c r="E92" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B93" s="11">
+        <v>0</v>
+      </c>
+      <c r="C93" s="11">
+        <v>0</v>
+      </c>
+      <c r="D93" s="11">
+        <v>0</v>
+      </c>
+      <c r="E93" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B94" s="9">
+        <v>0</v>
+      </c>
+      <c r="C94" s="9">
+        <v>0</v>
+      </c>
+      <c r="D94" s="9">
+        <v>0</v>
+      </c>
+      <c r="E94" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B95" s="11">
+        <v>0</v>
+      </c>
+      <c r="C95" s="11">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="19">
+        <v>2</v>
+      </c>
+      <c r="C96" s="19">
+        <v>4</v>
+      </c>
+      <c r="D96" s="19">
+        <v>1</v>
+      </c>
+      <c r="E96" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" customHeight="1" ht="15">
+      <c r="A97" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" customHeight="1" ht="22">
+      <c r="A99" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" customHeight="1" ht="20">
+      <c r="A100" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B101" s="9">
+        <v>5</v>
+      </c>
+      <c r="C101" s="9">
+        <v>2</v>
+      </c>
+      <c r="D101" s="21">
+        <v>3</v>
+      </c>
+      <c r="E101" s="22">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="11">
-        <v>4</v>
-      </c>
-      <c r="C15" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="13">
-        <v>8</v>
-      </c>
-      <c r="C16" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="11">
-        <v>0</v>
-      </c>
-      <c r="C17" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" customHeight="1" ht="32">
-      <c r="A19" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="15"/>
-    </row>
-    <row r="21" spans="1:3" customHeight="1" ht="32">
-      <c r="A21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="15"/>
+      <c r="B102" s="11">
+        <v>7</v>
+      </c>
+      <c r="C102" s="11">
+        <v>2</v>
+      </c>
+      <c r="D102" s="23">
+        <v>5</v>
+      </c>
+      <c r="E102" s="24">
+        <v>250.0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" customHeight="1" ht="15">
+      <c r="A103" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" customHeight="1" ht="32">
+      <c r="A105" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C105" s="26"/>
+    </row>
+    <row r="107" spans="1:5" customHeight="1" ht="32">
+      <c r="A107" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" s="26"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B107:C107"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.59055118110236" right="0.59055118110236" top="0.59055118110236" bottom="0.59055118110236" header="0.3" footer="0.3"/>
@@ -945,250 +2185,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="41" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12" customWidth="true" style="0"/>
+    <col min="3" max="3" width="13" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="42"/>
-    <row r="2" spans="1:3" customHeight="1" ht="24">
+    <row r="1" spans="1:5" customHeight="1" ht="42"/>
+    <row r="2" spans="1:5" customHeight="1" ht="24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" customHeight="1" ht="19">
+    <row r="3" spans="1:5" customHeight="1" ht="19">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" customHeight="1" ht="21">
+    <row r="4" spans="1:5" customHeight="1" ht="21">
       <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" customHeight="1" ht="18">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="18">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customHeight="1" ht="18">
+    <row r="6" spans="1:5" customHeight="1" ht="18">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customHeight="1" ht="18">
+    <row r="7" spans="1:5" customHeight="1" ht="18">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" customHeight="1" ht="22">
+    <row r="9" spans="1:5" customHeight="1" ht="22">
       <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" customHeight="1" ht="20">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="20">
       <c r="A10" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="12" t="s">
+      <c r="B11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" customHeight="1" ht="22">
+      <c r="B12" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="22">
       <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" customHeight="1" ht="20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="20">
       <c r="A15" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="22">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="20">
+      <c r="A21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" customHeight="1" ht="22">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" customHeight="1" ht="20">
-      <c r="A21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="B23" s="11">
+        <v>1</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="19">
+        <v>1</v>
+      </c>
+      <c r="C24" s="19">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="22">
+      <c r="A26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="20">
+      <c r="A27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="13">
+        <v>2</v>
+      </c>
+      <c r="C29" s="17">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="22">
+      <c r="A31" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="20">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" customHeight="1" ht="22">
-      <c r="A25" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customHeight="1" ht="20">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" customHeight="1" ht="22">
+      <c r="A40" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" customHeight="1" ht="20">
+      <c r="A41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="9">
+        <v>1</v>
+      </c>
+      <c r="C42" s="15">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="11">
+        <v>1</v>
+      </c>
+      <c r="C43" s="16">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="19">
+        <v>2</v>
+      </c>
+      <c r="C44" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" customHeight="1" ht="30">
+      <c r="A45" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" customHeight="1" ht="22">
+      <c r="A47" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" customHeight="1" ht="20">
+      <c r="A48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" customHeight="1" ht="22">
-      <c r="A33" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" customHeight="1" ht="20">
-      <c r="A34" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" customHeight="1" ht="32">
-      <c r="A38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="15"/>
-    </row>
-    <row r="40" spans="1:3" customHeight="1" ht="32">
-      <c r="A40" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="15"/>
+    <row r="49" spans="1:5">
+      <c r="A49" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" customHeight="1" ht="15">
+      <c r="A80" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" customHeight="1" ht="32">
+      <c r="A82" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" s="26"/>
+    </row>
+    <row r="84" spans="1:5" customHeight="1" ht="32">
+      <c r="A84" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" s="26"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B84:C84"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.59055118110236" right="0.59055118110236" top="0.59055118110236" bottom="0.59055118110236" header="0.3" footer="0.3"/>
@@ -1206,282 +2819,661 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="41" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12" customWidth="true" style="0"/>
+    <col min="3" max="3" width="13" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="42"/>
-    <row r="2" spans="1:3" customHeight="1" ht="24">
+    <row r="1" spans="1:5" customHeight="1" ht="42"/>
+    <row r="2" spans="1:5" customHeight="1" ht="24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" customHeight="1" ht="19">
+    <row r="3" spans="1:5" customHeight="1" ht="19">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" customHeight="1" ht="21">
+    <row r="4" spans="1:5" customHeight="1" ht="21">
       <c r="A4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" customHeight="1" ht="18">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="18">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customHeight="1" ht="18">
+    <row r="6" spans="1:5" customHeight="1" ht="18">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customHeight="1" ht="18">
+    <row r="7" spans="1:5" customHeight="1" ht="18">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" customHeight="1" ht="22">
+    <row r="9" spans="1:5" customHeight="1" ht="22">
       <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" customHeight="1" ht="20">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="20">
       <c r="A10" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="12" t="s">
+      <c r="B11" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" customHeight="1" ht="22">
+      <c r="B12" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="22">
       <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" customHeight="1" ht="20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="20">
       <c r="A15" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="22">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="20">
+      <c r="A21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B23" s="11">
+        <v>2</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="19">
+        <v>2</v>
+      </c>
+      <c r="C24" s="19">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="9">
+    <row r="26" spans="1:5" customHeight="1" ht="22">
+      <c r="A26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="20">
+      <c r="A27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="11">
+        <v>1</v>
+      </c>
+      <c r="C29" s="16">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1</v>
+      </c>
+      <c r="C30" s="15">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="13">
+        <v>4</v>
+      </c>
+      <c r="C31" s="17">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="22">
+      <c r="A33" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" customHeight="1" ht="20">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" customHeight="1" ht="22">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" customHeight="1" ht="20">
-      <c r="A21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" customHeight="1" ht="22">
+      <c r="A44" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" customHeight="1" ht="20">
+      <c r="A45" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" customHeight="1" ht="22">
-      <c r="A25" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customHeight="1" ht="20">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="B45" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="9">
+        <v>2</v>
+      </c>
+      <c r="C46" s="15">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="11">
+        <v>1</v>
+      </c>
+      <c r="C47" s="16">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="19">
+        <v>3</v>
+      </c>
+      <c r="C48" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" customHeight="1" ht="30">
+      <c r="A49" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" customHeight="1" ht="22">
+      <c r="A51" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" customHeight="1" ht="20">
+      <c r="A52" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" customHeight="1" ht="22">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" customHeight="1" ht="20">
-      <c r="A38" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" customHeight="1" ht="32">
-      <c r="A42" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="44" spans="1:3" customHeight="1" ht="32">
-      <c r="A44" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="15"/>
+    <row r="53" spans="1:5">
+      <c r="A53" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" customHeight="1" ht="15">
+      <c r="A84" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" customHeight="1" ht="32">
+      <c r="A86" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="26"/>
+    </row>
+    <row r="88" spans="1:5" customHeight="1" ht="32">
+      <c r="A88" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="26"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B88:C88"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.59055118110236" right="0.59055118110236" top="0.59055118110236" bottom="0.59055118110236" header="0.3" footer="0.3"/>
@@ -1499,202 +3491,621 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="41" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12" customWidth="true" style="0"/>
+    <col min="3" max="3" width="13" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="42"/>
-    <row r="2" spans="1:3" customHeight="1" ht="24">
+    <row r="1" spans="1:5" customHeight="1" ht="42"/>
+    <row r="2" spans="1:5" customHeight="1" ht="24">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" customHeight="1" ht="19">
+    <row r="3" spans="1:5" customHeight="1" ht="19">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" customHeight="1" ht="21">
+    <row r="4" spans="1:5" customHeight="1" ht="21">
       <c r="A4" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" customHeight="1" ht="18">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="18">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customHeight="1" ht="18">
+    <row r="6" spans="1:5" customHeight="1" ht="18">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customHeight="1" ht="18">
+    <row r="7" spans="1:5" customHeight="1" ht="18">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" customHeight="1" ht="22">
+    <row r="9" spans="1:5" customHeight="1" ht="22">
       <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" customHeight="1" ht="20">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="20">
       <c r="A10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="22">
+      <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" customHeight="1" ht="22">
-      <c r="A14" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" customHeight="1" ht="20">
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="20">
       <c r="A15" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="22">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="20">
+      <c r="A21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="12" t="s">
+      <c r="B23" s="11">
+        <v>0</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" customHeight="1" ht="22">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" customHeight="1" ht="20">
-      <c r="A21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="B24" s="9">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="22">
+      <c r="A27" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="20">
+      <c r="A28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="9">
+        <v>1</v>
+      </c>
+      <c r="C29" s="15">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="13">
+        <v>1</v>
+      </c>
+      <c r="C30" s="17">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="22">
+      <c r="A32" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="20">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" customHeight="1" ht="22">
-      <c r="A25" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customHeight="1" ht="20">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="7" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" customHeight="1" ht="22">
+      <c r="A39" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" customHeight="1" ht="20">
+      <c r="A40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="9">
+        <v>1</v>
+      </c>
+      <c r="C41" s="15">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="11">
+        <v>0</v>
+      </c>
+      <c r="C42" s="16">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="19">
+        <v>1</v>
+      </c>
+      <c r="C43" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" customHeight="1" ht="30">
+      <c r="A44" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" customHeight="1" ht="22">
+      <c r="A46" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" customHeight="1" ht="20">
+      <c r="A47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" customHeight="1" ht="22">
-      <c r="A29" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" customHeight="1" ht="20">
-      <c r="A30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" customHeight="1" ht="32">
-      <c r="A32" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="15"/>
-    </row>
-    <row r="34" spans="1:3" customHeight="1" ht="32">
-      <c r="A34" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="15"/>
+    <row r="48" spans="1:5">
+      <c r="A48" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" customHeight="1" ht="15">
+      <c r="A79" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" customHeight="1" ht="32">
+      <c r="A81" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" s="26"/>
+    </row>
+    <row r="83" spans="1:5" customHeight="1" ht="32">
+      <c r="A83" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="26"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B83:C83"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.59055118110236" right="0.59055118110236" top="0.59055118110236" bottom="0.59055118110236" header="0.3" footer="0.3"/>
